--- a/salidas/empresas/CAT.xlsx
+++ b/salidas/empresas/CAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>40.99883270263672</v>
+        <v>40.99885177612305</v>
       </c>
       <c r="C2" t="n">
         <v>67.90000152587891</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>44.12660598754883</v>
+        <v>44.12657928466797</v>
       </c>
       <c r="C3" t="n">
         <v>73.08000183105469</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>43.3597526550293</v>
+        <v>43.3597297668457</v>
       </c>
       <c r="C4" t="n">
         <v>71.80999755859375</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>45.87797546386719</v>
+        <v>45.87798690795898</v>
       </c>
       <c r="C5" t="n">
         <v>75.73999786376953</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>44.18796920776367</v>
+        <v>44.18798828125</v>
       </c>
       <c r="C6" t="n">
         <v>72.94999694824219</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>45.11474227905273</v>
+        <v>45.1147575378418</v>
       </c>
       <c r="C7" t="n">
         <v>74.48000335693359</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>43.11500549316406</v>
+        <v>43.11500930786133</v>
       </c>
       <c r="C8" t="n">
         <v>70.87000274658203</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.03057098388672</v>
+        <v>40.03057861328125</v>
       </c>
       <c r="C10" t="n">
         <v>65.80000305175781</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>37.09509658813477</v>
+        <v>37.0950927734375</v>
       </c>
       <c r="C11" t="n">
         <v>60.70999908447266</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>37.90163040161133</v>
+        <v>37.90162658691406</v>
       </c>
       <c r="C12" t="n">
         <v>62.02999877929688</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>37.47392654418945</v>
+        <v>37.47391510009766</v>
       </c>
       <c r="C13" t="n">
         <v>61.33000183105469</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>39.34514236450195</v>
+        <v>39.34513854980469</v>
       </c>
       <c r="C14" t="n">
         <v>64.06999969482422</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>39.56621170043945</v>
+        <v>39.56621551513672</v>
       </c>
       <c r="C15" t="n">
         <v>64.43000030517578</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>41.16287994384766</v>
+        <v>41.16287612915039</v>
       </c>
       <c r="C16" t="n">
         <v>67.02999877929688</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>48.46528625488281</v>
+        <v>48.46529006958008</v>
       </c>
       <c r="C18" t="n">
         <v>78.58000183105469</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>48.29258728027344</v>
+        <v>48.29256820678711</v>
       </c>
       <c r="C19" t="n">
         <v>78.30000305175781</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>48.80415344238281</v>
+        <v>48.80414962768555</v>
       </c>
       <c r="C20" t="n">
         <v>78.80000305175781</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>46.92753219604492</v>
+        <v>46.92755126953125</v>
       </c>
       <c r="C21" t="n">
         <v>75.76999664306641</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>48.57498931884766</v>
+        <v>48.57499313354492</v>
       </c>
       <c r="C22" t="n">
         <v>78.43000030517578</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>46.42578887939453</v>
+        <v>46.4257926940918</v>
       </c>
       <c r="C23" t="n">
         <v>74.61000061035156</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>44.73952865600586</v>
+        <v>44.7395133972168</v>
       </c>
       <c r="C24" t="n">
         <v>71.90000152587891</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>45.15017318725586</v>
+        <v>45.15018844604492</v>
       </c>
       <c r="C25" t="n">
         <v>72.55999755859375</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>44.42206954956055</v>
+        <v>44.42210006713867</v>
       </c>
       <c r="C26" t="n">
         <v>70.98999786376953</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>45.26059722900391</v>
+        <v>45.26060485839844</v>
       </c>
       <c r="C27" t="n">
         <v>72.33000183105469</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>48.99008560180664</v>
+        <v>48.99005889892578</v>
       </c>
       <c r="C28" t="n">
         <v>78.29000091552734</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>51.47100448608398</v>
+        <v>51.47099685668945</v>
       </c>
       <c r="C29" t="n">
         <v>81.87999725341797</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>51.94878005981445</v>
+        <v>51.94875335693359</v>
       </c>
       <c r="C30" t="n">
         <v>82.63999938964844</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>43.9631233215332</v>
+        <v>43.96310424804688</v>
       </c>
       <c r="C32" t="n">
         <v>69.51999664306641</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>44.72830581665039</v>
+        <v>44.72830200195312</v>
       </c>
       <c r="C33" t="n">
         <v>70.73000335693359</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.68989944458008</v>
+        <v>37.68990325927734</v>
       </c>
       <c r="C34" t="n">
         <v>59.59999847412109</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>24.40061187744141</v>
+        <v>24.40060615539551</v>
       </c>
       <c r="C35" t="n">
         <v>38.20000076293945</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>26.18275260925293</v>
+        <v>26.18275451660156</v>
       </c>
       <c r="C36" t="n">
         <v>40.9900016784668</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>28.53338813781738</v>
+        <v>28.53339195251465</v>
       </c>
       <c r="C37" t="n">
         <v>44.66999816894531</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.9183235168457</v>
+        <v>19.91831970214844</v>
       </c>
       <c r="C38" t="n">
         <v>30.85000038146973</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.88946437835693</v>
+        <v>15.88946151733398</v>
       </c>
       <c r="C39" t="n">
         <v>24.61000061035156</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>18.05239486694336</v>
+        <v>18.05238914489746</v>
       </c>
       <c r="C40" t="n">
         <v>27.95999908447266</v>
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>23.18973922729492</v>
+        <v>23.18974113464355</v>
       </c>
       <c r="C42" t="n">
         <v>35.45999908447266</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.60713768005371</v>
+        <v>21.60713386535645</v>
       </c>
       <c r="C43" t="n">
         <v>33.04000091552734</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>29.17598342895508</v>
+        <v>29.17598915100098</v>
       </c>
       <c r="C44" t="n">
         <v>44.06000137329102</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>30.00371932983398</v>
+        <v>30.00370979309082</v>
       </c>
       <c r="C45" t="n">
         <v>45.31000137329102</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>33.99009323120117</v>
+        <v>33.99009704589844</v>
       </c>
       <c r="C46" t="n">
         <v>51.33000183105469</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>36.72414016723633</v>
+        <v>36.72415924072266</v>
       </c>
       <c r="C47" t="n">
         <v>55.06000137329102</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>38.94522476196289</v>
+        <v>38.94521331787109</v>
       </c>
       <c r="C48" t="n">
         <v>58.38999938964844</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>38.01143646240234</v>
+        <v>38.01145553588867</v>
       </c>
       <c r="C49" t="n">
         <v>56.9900016784668</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>35.08097839355469</v>
+        <v>35.08098602294922</v>
       </c>
       <c r="C50" t="n">
         <v>52.2400016784668</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>38.31108093261719</v>
+        <v>38.31106567382812</v>
       </c>
       <c r="C51" t="n">
         <v>57.04999923706055</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.20597076416016</v>
+        <v>42.20597457885742</v>
       </c>
       <c r="C52" t="n">
         <v>62.84999847412109</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>46.01004409790039</v>
+        <v>46.01004791259766</v>
       </c>
       <c r="C53" t="n">
         <v>68.08999633789062</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>41.05698776245117</v>
+        <v>41.05697631835938</v>
       </c>
       <c r="C54" t="n">
         <v>60.7599983215332</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.59073257446289</v>
+        <v>40.59073638916016</v>
       </c>
       <c r="C55" t="n">
         <v>60.06999969482422</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>47.44559860229492</v>
+        <v>47.44561767578125</v>
       </c>
       <c r="C56" t="n">
         <v>69.75</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>44.32339096069336</v>
+        <v>44.32339477539062</v>
       </c>
       <c r="C57" t="n">
         <v>65.16000366210938</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>53.52001953125</v>
+        <v>53.52002716064453</v>
       </c>
       <c r="C58" t="n">
         <v>78.68000030517578</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>53.76011657714844</v>
+        <v>53.76010513305664</v>
       </c>
       <c r="C59" t="n">
         <v>78.59999847412109</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>57.86392593383789</v>
+        <v>57.86393356323242</v>
       </c>
       <c r="C60" t="n">
         <v>84.59999847412109</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>64.06069183349609</v>
+        <v>64.06070709228516</v>
       </c>
       <c r="C61" t="n">
         <v>93.66000366210938</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>66.66400146484375</v>
+        <v>66.66401672363281</v>
       </c>
       <c r="C62" t="n">
         <v>97.01000213623047</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>70.73217010498047</v>
+        <v>70.73215484619141</v>
       </c>
       <c r="C63" t="n">
         <v>102.9300003051758</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>76.51827239990234</v>
+        <v>76.51828002929688</v>
       </c>
       <c r="C64" t="n">
         <v>111.3499984741211</v>
@@ -1807,7 +1819,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>73.00717163085938</v>
+        <v>73.00715637207031</v>
       </c>
       <c r="C66" t="n">
         <v>105.8000030517578</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>73.46260833740234</v>
+        <v>73.46257781982422</v>
       </c>
       <c r="C67" t="n">
         <v>106.4599990844727</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>68.45785522460938</v>
+        <v>68.45787811279297</v>
       </c>
       <c r="C68" t="n">
         <v>98.79000091552734</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>63.05966949462891</v>
+        <v>63.05968475341797</v>
       </c>
       <c r="C69" t="n">
         <v>91</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>51.16843795776367</v>
+        <v>51.16843032836914</v>
       </c>
       <c r="C70" t="n">
         <v>73.83999633789062</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>65.81967163085938</v>
+        <v>65.81967926025391</v>
       </c>
       <c r="C71" t="n">
         <v>94.45999908447266</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>68.20273590087891</v>
+        <v>68.20272827148438</v>
       </c>
       <c r="C72" t="n">
         <v>97.87999725341797</v>
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>76.37461853027344</v>
+        <v>76.37464904785156</v>
       </c>
       <c r="C74" t="n">
         <v>109.120002746582</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>79.93717193603516</v>
+        <v>79.93720245361328</v>
       </c>
       <c r="C75" t="n">
         <v>114.2099990844727</v>
@@ -2126,7 +2138,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>72.23442077636719</v>
+        <v>72.23445129394531</v>
       </c>
       <c r="C77" t="n">
         <v>102.7699966430664</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>61.58588027954102</v>
+        <v>61.58587646484375</v>
       </c>
       <c r="C78" t="n">
         <v>87.62000274658203</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>59.68109512329102</v>
+        <v>59.68108749389648</v>
       </c>
       <c r="C79" t="n">
         <v>84.91000366210938</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>59.56724548339844</v>
+        <v>59.56725311279297</v>
       </c>
       <c r="C80" t="n">
         <v>84.20999908447266</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>60.35947036743164</v>
+        <v>60.35947799682617</v>
       </c>
       <c r="C81" t="n">
         <v>85.33000183105469</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>60.86171722412109</v>
+        <v>60.86172103881836</v>
       </c>
       <c r="C82" t="n">
         <v>86.04000091552734</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>60.35393142700195</v>
+        <v>60.35394668579102</v>
       </c>
       <c r="C83" t="n">
         <v>84.80999755859375</v>
@@ -2358,7 +2370,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>64.13712310791016</v>
+        <v>64.13713073730469</v>
       </c>
       <c r="C85" t="n">
         <v>89.61000061035156</v>
@@ -2416,7 +2428,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>66.11259460449219</v>
+        <v>66.11255645751953</v>
       </c>
       <c r="C87" t="n">
         <v>92.37000274658203</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>62.24758148193359</v>
+        <v>62.24761581420898</v>
       </c>
       <c r="C88" t="n">
         <v>86.97000122070312</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>59.42033767700195</v>
+        <v>59.42037582397461</v>
       </c>
       <c r="C91" t="n">
         <v>82.48999786376953</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>60.13923645019531</v>
+        <v>60.13925170898438</v>
       </c>
       <c r="C92" t="n">
         <v>82.91000366210938</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>59.87085723876953</v>
+        <v>59.8708610534668</v>
       </c>
       <c r="C93" t="n">
         <v>82.54000091552734</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>60.49465179443359</v>
+        <v>60.49466705322266</v>
       </c>
       <c r="C94" t="n">
         <v>83.40000152587891</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>60.88910675048828</v>
+        <v>60.88914108276367</v>
       </c>
       <c r="C95" t="n">
         <v>83.36000061035156</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>61.79485702514648</v>
+        <v>61.79486846923828</v>
       </c>
       <c r="C96" t="n">
         <v>84.59999847412109</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>66.33085632324219</v>
+        <v>66.33084869384766</v>
       </c>
       <c r="C97" t="n">
         <v>90.80999755859375</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>69.04350280761719</v>
+        <v>69.04351806640625</v>
       </c>
       <c r="C98" t="n">
         <v>93.91000366210938</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>71.29325103759766</v>
+        <v>71.29322814941406</v>
       </c>
       <c r="C99" t="n">
         <v>96.97000122070312</v>
@@ -2822,7 +2834,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>77.94734954833984</v>
+        <v>77.94732666015625</v>
       </c>
       <c r="C101" t="n">
         <v>105.4000015258789</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>75.60301971435547</v>
+        <v>75.60299682617188</v>
       </c>
       <c r="C102" t="n">
         <v>102.2300033569336</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>80.36562347412109</v>
+        <v>80.36560821533203</v>
       </c>
       <c r="C103" t="n">
         <v>108.6699981689453</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.97962951660156</v>
+        <v>74.97963714599609</v>
       </c>
       <c r="C104" t="n">
         <v>100.75</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>81.17148590087891</v>
+        <v>81.17146301269531</v>
       </c>
       <c r="C105" t="n">
         <v>109.0699996948242</v>
@@ -2996,7 +3008,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.04573059082031</v>
+        <v>76.04573822021484</v>
       </c>
       <c r="C107" t="n">
         <v>101.4100036621094</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>75.43832397460938</v>
+        <v>75.43834686279297</v>
       </c>
       <c r="C108" t="n">
         <v>100.5999984741211</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>68.63688659667969</v>
+        <v>68.63686370849609</v>
       </c>
       <c r="C109" t="n">
         <v>91.52999877929688</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>60.45994567871094</v>
+        <v>60.45993041992188</v>
       </c>
       <c r="C110" t="n">
         <v>79.97000122070312</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>62.67511749267578</v>
+        <v>62.67512512207031</v>
       </c>
       <c r="C111" t="n">
         <v>82.90000152587891</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>60.50531005859375</v>
+        <v>60.50528335571289</v>
       </c>
       <c r="C112" t="n">
         <v>80.02999877929688</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>66.22849273681641</v>
+        <v>66.22850036621094</v>
       </c>
       <c r="C113" t="n">
         <v>86.87999725341797</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>65.03929901123047</v>
+        <v>65.03931427001953</v>
       </c>
       <c r="C114" t="n">
         <v>85.31999969482422</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>64.65816497802734</v>
+        <v>64.65815734863281</v>
       </c>
       <c r="C115" t="n">
         <v>84.81999969482422</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>60.49300003051758</v>
+        <v>60.49299621582031</v>
       </c>
       <c r="C116" t="n">
         <v>78.62999725341797</v>
@@ -3315,7 +3327,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>50.28389358520508</v>
+        <v>50.28390502929688</v>
       </c>
       <c r="C118" t="n">
         <v>65.36000061035156</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.78148651123047</v>
+        <v>56.78149795532227</v>
       </c>
       <c r="C119" t="n">
         <v>72.98999786376953</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>56.51700973510742</v>
+        <v>56.51700210571289</v>
       </c>
       <c r="C120" t="n">
         <v>72.65000152587891</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>52.86849212646484</v>
+        <v>52.86847686767578</v>
       </c>
       <c r="C121" t="n">
         <v>67.95999908447266</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>49.02489471435547</v>
+        <v>49.02490615844727</v>
       </c>
       <c r="C122" t="n">
         <v>62.2400016784668</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>53.32562255859375</v>
+        <v>53.32561492919922</v>
       </c>
       <c r="C123" t="n">
         <v>67.69999694824219</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.28866577148438</v>
+        <v>60.28867721557617</v>
       </c>
       <c r="C124" t="n">
         <v>76.54000091552734</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>61.81504440307617</v>
+        <v>61.81502151489258</v>
       </c>
       <c r="C125" t="n">
         <v>77.72000122070312</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.67123413085938</v>
+        <v>57.67125701904297</v>
       </c>
       <c r="C126" t="n">
         <v>72.51000213623047</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.29589462280273</v>
+        <v>60.2959098815918</v>
       </c>
       <c r="C127" t="n">
         <v>75.80999755859375</v>
@@ -3634,7 +3646,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>65.80726623535156</v>
+        <v>65.80729675292969</v>
       </c>
       <c r="C129" t="n">
         <v>81.94999694824219</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>71.28387451171875</v>
+        <v>71.28386688232422</v>
       </c>
       <c r="C130" t="n">
         <v>88.76999664306641</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>67.61143493652344</v>
+        <v>67.61146545410156</v>
       </c>
       <c r="C131" t="n">
         <v>83.45999908447266</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>77.41374969482422</v>
+        <v>77.41372680664062</v>
       </c>
       <c r="C132" t="n">
         <v>95.55999755859375</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>75.12922668457031</v>
+        <v>75.12923431396484</v>
       </c>
       <c r="C133" t="n">
         <v>92.73999786376953</v>
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>78.95461273193359</v>
+        <v>78.95457458496094</v>
       </c>
       <c r="C135" t="n">
         <v>96.66000366210938</v>
@@ -3864,7 +3876,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3891,11 +3903,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>84.22264099121094</v>
+        <v>84.22264862060547</v>
       </c>
       <c r="C137" t="n">
         <v>102.2600021362305</v>
@@ -3918,11 +3930,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>86.83350372314453</v>
+        <v>86.83349609375</v>
       </c>
       <c r="C138" t="n">
         <v>105.4300003051758</v>
@@ -3945,11 +3957,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>88.50544738769531</v>
+        <v>88.50541687011719</v>
       </c>
       <c r="C139" t="n">
         <v>107.4599990844727</v>
@@ -3972,11 +3984,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>94.52809143066406</v>
+        <v>94.52809906005859</v>
       </c>
       <c r="C140" t="n">
         <v>113.9499969482422</v>
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>97.46473693847656</v>
+        <v>97.46475219726562</v>
       </c>
       <c r="C141" t="n">
         <v>117.4899978637695</v>
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>103.4541473388672</v>
+        <v>103.4541397094727</v>
       </c>
       <c r="C142" t="n">
         <v>124.7099990844727</v>
@@ -4057,7 +4069,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4086,11 +4098,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>117.7905120849609</v>
+        <v>117.7904815673828</v>
       </c>
       <c r="C144" t="n">
         <v>141.1499938964844</v>
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>131.5014343261719</v>
+        <v>131.5013885498047</v>
       </c>
       <c r="C145" t="n">
         <v>157.5800018310547</v>
@@ -4144,11 +4156,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>136.4713592529297</v>
+        <v>136.4713134765625</v>
       </c>
       <c r="C146" t="n">
         <v>162.7799987792969</v>
@@ -4173,11 +4185,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>129.6385192871094</v>
+        <v>129.6385040283203</v>
       </c>
       <c r="C147" t="n">
         <v>154.6300048828125</v>
@@ -4202,11 +4214,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>123.5603332519531</v>
+        <v>123.5603256225586</v>
       </c>
       <c r="C148" t="n">
         <v>147.3800048828125</v>
@@ -4231,7 +4243,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4260,11 +4272,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>127.9994049072266</v>
+        <v>127.9993743896484</v>
       </c>
       <c r="C150" t="n">
         <v>151.9100036621094</v>
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>114.3155288696289</v>
+        <v>114.3155746459961</v>
       </c>
       <c r="C151" t="n">
         <v>135.6699981689453</v>
@@ -4318,7 +4330,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4347,11 +4359,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>117.7123641967773</v>
+        <v>117.7123718261719</v>
       </c>
       <c r="C153" t="n">
         <v>138.8500061035156</v>
@@ -4376,7 +4388,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4405,7 +4417,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4434,7 +4446,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4463,7 +4475,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>114.3389511108398</v>
+        <v>114.3389205932617</v>
       </c>
       <c r="C158" t="n">
         <v>133.1600036621094</v>
@@ -4521,11 +4533,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>117.9281463623047</v>
+        <v>117.9281005859375</v>
       </c>
       <c r="C159" t="n">
         <v>137.3399963378906</v>
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>116.3396148681641</v>
+        <v>116.3396301269531</v>
       </c>
       <c r="C160" t="n">
         <v>135.4900054931641</v>
@@ -4579,11 +4591,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>120.4397888183594</v>
+        <v>120.4397659301758</v>
       </c>
       <c r="C161" t="n">
         <v>139.4199981689453</v>
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>103.4994049072266</v>
+        <v>103.4994125366211</v>
       </c>
       <c r="C162" t="n">
         <v>119.8099975585938</v>
@@ -4637,7 +4649,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4666,11 +4678,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>114.6200790405273</v>
+        <v>114.6200561523438</v>
       </c>
       <c r="C164" t="n">
         <v>131.6699981689453</v>
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>103.590705871582</v>
+        <v>103.590690612793</v>
       </c>
       <c r="C165" t="n">
         <v>119</v>
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>109.9541473388672</v>
+        <v>109.9541397094727</v>
       </c>
       <c r="C166" t="n">
         <v>126.3099975585938</v>
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>120.899169921875</v>
+        <v>120.8991851806641</v>
       </c>
       <c r="C167" t="n">
         <v>137.8000030517578</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>126.9791870117188</v>
+        <v>126.9792633056641</v>
       </c>
       <c r="C168" t="n">
         <v>144.7299957275391</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>129.5674133300781</v>
+        <v>129.5673980712891</v>
       </c>
       <c r="C169" t="n">
         <v>147.6799926757812</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>116.0485763549805</v>
+        <v>116.0485992431641</v>
       </c>
       <c r="C170" t="n">
         <v>131.3500061035156</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>109.7668380737305</v>
+        <v>109.7668685913086</v>
       </c>
       <c r="C171" t="n">
         <v>124.2399978637695</v>
@@ -4898,11 +4910,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>102.5221176147461</v>
+        <v>102.5221099853516</v>
       </c>
       <c r="C172" t="n">
         <v>116.0400009155273</v>
@@ -4927,11 +4939,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>103.7665176391602</v>
+        <v>103.7664947509766</v>
       </c>
       <c r="C173" t="n">
         <v>116.379997253418</v>
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>107.1100692749023</v>
+        <v>107.1100540161133</v>
       </c>
       <c r="C174" t="n">
         <v>120.129997253418</v>
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>112.7896881103516</v>
+        <v>112.7896575927734</v>
       </c>
       <c r="C175" t="n">
         <v>126.5</v>
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>119.3655090332031</v>
+        <v>119.3655319213867</v>
       </c>
       <c r="C176" t="n">
         <v>132.8800048828125</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>127.83642578125</v>
+        <v>127.8364334106445</v>
       </c>
       <c r="C177" t="n">
         <v>142.3099975585938</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>133.9807586669922</v>
+        <v>133.9807739257812</v>
       </c>
       <c r="C178" t="n">
         <v>149.1499938964844</v>
@@ -5101,7 +5113,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>156.8875732421875</v>
+        <v>156.8875885009766</v>
       </c>
       <c r="C180" t="n">
         <v>173.5899963378906</v>
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>164.5065002441406</v>
+        <v>164.5065155029297</v>
       </c>
       <c r="C181" t="n">
         <v>182.0200042724609</v>
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>166.1267395019531</v>
+        <v>166.1268005371094</v>
       </c>
       <c r="C182" t="n">
         <v>182.8399963378906</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>196.1466369628906</v>
+        <v>196.1466217041016</v>
       </c>
       <c r="C183" t="n">
         <v>215.8800048828125</v>
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>210.6749725341797</v>
+        <v>210.6750183105469</v>
       </c>
       <c r="C184" t="n">
         <v>231.8699951171875</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>208.1955413818359</v>
+        <v>208.1955718994141</v>
       </c>
       <c r="C185" t="n">
         <v>228.1100006103516</v>
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>220.0332641601562</v>
+        <v>220.0332489013672</v>
       </c>
       <c r="C186" t="n">
         <v>241.0800018310547</v>
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>198.6304779052734</v>
+        <v>198.6305084228516</v>
       </c>
       <c r="C187" t="n">
         <v>217.6300048828125</v>
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>189.7129974365234</v>
+        <v>189.7129821777344</v>
       </c>
       <c r="C188" t="n">
         <v>206.75</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>193.4934692382812</v>
+        <v>193.4934844970703</v>
       </c>
       <c r="C189" t="n">
         <v>210.8699951171875</v>
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>176.1509246826172</v>
+        <v>176.1509094238281</v>
       </c>
       <c r="C190" t="n">
         <v>191.9700012207031</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>188.2323760986328</v>
+        <v>188.2323608398438</v>
       </c>
       <c r="C191" t="n">
         <v>204.0099945068359</v>
@@ -5478,11 +5490,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>178.3968353271484</v>
+        <v>178.3968200683594</v>
       </c>
       <c r="C192" t="n">
         <v>193.3500061035156</v>
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>190.7512817382812</v>
+        <v>190.7512969970703</v>
       </c>
       <c r="C193" t="n">
         <v>206.7400054931641</v>
@@ -5536,11 +5548,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>186.8742523193359</v>
+        <v>186.8742218017578</v>
       </c>
       <c r="C194" t="n">
         <v>201.5599975585938</v>
@@ -5565,7 +5577,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5594,11 +5606,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>206.5852508544922</v>
+        <v>206.5852355957031</v>
       </c>
       <c r="C196" t="n">
         <v>222.8200073242188</v>
@@ -5623,7 +5635,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>201.0828094482422</v>
+        <v>201.0827941894531</v>
       </c>
       <c r="C198" t="n">
         <v>215.8500061035156</v>
@@ -5681,11 +5693,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>166.5302734375</v>
+        <v>166.5302886962891</v>
       </c>
       <c r="C199" t="n">
         <v>178.7599945068359</v>
@@ -5710,11 +5722,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>185.9732360839844</v>
+        <v>185.9732666015625</v>
       </c>
       <c r="C200" t="n">
         <v>198.25</v>
@@ -5739,11 +5751,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>173.2717437744141</v>
+        <v>173.271728515625</v>
       </c>
       <c r="C201" t="n">
         <v>184.7100067138672</v>
@@ -5768,11 +5780,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>153.9192352294922</v>
+        <v>153.9192504882812</v>
       </c>
       <c r="C202" t="n">
         <v>164.0800018310547</v>
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>204.4142608642578</v>
+        <v>204.4142913818359</v>
       </c>
       <c r="C203" t="n">
         <v>216.4600067138672</v>
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>223.2541046142578</v>
+        <v>223.2540740966797</v>
       </c>
       <c r="C204" t="n">
         <v>236.4100036621094</v>
@@ -5855,11 +5867,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>226.2287750244141</v>
+        <v>226.2287902832031</v>
       </c>
       <c r="C205" t="n">
         <v>239.5599975585938</v>
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>239.3865661621094</v>
+        <v>239.3865814208984</v>
       </c>
       <c r="C206" t="n">
         <v>252.2899932861328</v>
@@ -5913,7 +5925,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5942,7 +5954,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5971,7 +5983,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6000,7 +6012,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6029,7 +6041,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>254.2264099121094</v>
+        <v>254.2264251708984</v>
       </c>
       <c r="C212" t="n">
         <v>265.1700134277344</v>
@@ -6087,7 +6099,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6116,7 +6128,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6145,7 +6157,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6174,7 +6186,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6203,7 +6215,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6232,11 +6244,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>290.7446594238281</v>
+        <v>290.74462890625</v>
       </c>
       <c r="C218" t="n">
         <v>300.3099975585938</v>
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>323.3228454589844</v>
+        <v>323.3228149414062</v>
       </c>
       <c r="C219" t="n">
         <v>333.9599914550781</v>
@@ -6290,7 +6302,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6319,11 +6331,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>325.0941772460938</v>
+        <v>325.0941467285156</v>
       </c>
       <c r="C221" t="n">
         <v>334.5700073242188</v>
@@ -6348,11 +6360,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>328.9322814941406</v>
+        <v>328.9322509765625</v>
       </c>
       <c r="C222" t="n">
         <v>338.5199890136719</v>
@@ -6377,7 +6389,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6406,11 +6418,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>337.7648010253906</v>
+        <v>337.7647399902344</v>
       </c>
       <c r="C224" t="n">
         <v>346.2000122070312</v>
@@ -6435,11 +6447,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>347.4234924316406</v>
+        <v>347.423583984375</v>
       </c>
       <c r="C225" t="n">
         <v>356.1000061035156</v>
@@ -6464,11 +6476,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>381.5902709960938</v>
+        <v>381.5903015136719</v>
       </c>
       <c r="C226" t="n">
         <v>391.1199951171875</v>
@@ -6493,11 +6505,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>368.3525085449219</v>
+        <v>368.3524780273438</v>
       </c>
       <c r="C227" t="n">
         <v>376.2000122070312</v>
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>397.6385498046875</v>
+        <v>397.6385192871094</v>
       </c>
       <c r="C228" t="n">
         <v>406.1099853515625</v>
@@ -6551,11 +6563,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>355.19287109375</v>
+        <v>355.1928405761719</v>
       </c>
       <c r="C229" t="n">
         <v>362.760009765625</v>
@@ -6580,11 +6592,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>365.0250549316406</v>
+        <v>365.0250854492188</v>
       </c>
       <c r="C230" t="n">
         <v>371.4400024414062</v>
@@ -6609,11 +6621,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>338.0098571777344</v>
+        <v>338.0098876953125</v>
       </c>
       <c r="C231" t="n">
         <v>343.9500122070312</v>
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>324.1041870117188</v>
+        <v>324.1042175292969</v>
       </c>
       <c r="C232" t="n">
         <v>329.7999877929688</v>
@@ -6667,7 +6679,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6696,7 +6708,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6725,7 +6737,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6754,11 +6766,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>434.1122741699219</v>
+        <v>434.1123046875</v>
       </c>
       <c r="C236" t="n">
         <v>438.0199890136719</v>
@@ -6783,7 +6795,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6841,11 +6853,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>573.7537841796875</v>
+        <v>573.7538452148438</v>
       </c>
       <c r="C239" t="n">
         <v>577.260009765625</v>
@@ -6870,7 +6882,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6928,11 +6940,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>654.89599609375</v>
+        <v>654.8959350585938</v>
       </c>
       <c r="C242" t="n">
         <v>657.3599853515625</v>
@@ -6957,11 +6969,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>740.045654296875</v>
+        <v>740.0455932617188</v>
       </c>
       <c r="C243" t="n">
         <v>742.8300170898438</v>
@@ -6986,11 +6998,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>705.8045043945312</v>
+        <v>705.804443359375</v>
       </c>
       <c r="C244" t="n">
         <v>708.4600219726562</v>
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>812.02001953125</v>
+        <v>805.25</v>
       </c>
       <c r="C250" t="n">
-        <v>812.02001953125</v>
+        <v>805.25</v>
       </c>
       <c r="D250" t="n">
-        <v>39204200</v>
+        <v>41402000</v>
       </c>
       <c r="E250" t="n">
         <v>23.23</v>
       </c>
       <c r="F250" t="n">
-        <v>34.95566162424667</v>
+        <v>34.66422729229445</v>
       </c>
       <c r="G250" t="n">
         <v>459674889</v>
       </c>
       <c r="H250" t="n">
-        <v>373265212343.8052</v>
+        <v>370153204367.25</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08528679929697008</v>
+        <v>0.09006800456311199</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40037</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40037</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I7" t="n">
         <v>1.41</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="K7" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I8" t="n">
         <v>1.96</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="K8" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I9" t="n">
         <v>2.45</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="K9" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I10" t="n">
         <v>3.03</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="K10" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I11" t="n">
         <v>4.14</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="K11" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I12" t="n">
         <v>5.62</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K12" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I13" t="n">
         <v>6.049999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K13" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I14" t="n">
         <v>6.539999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I15" t="n">
         <v>7.39</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="K15" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I16" t="n">
         <v>7.92</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K16" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I17" t="n">
         <v>8.94</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K17" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I18" t="n">
         <v>9.77</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I19" t="n">
         <v>8.49</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="K19" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I20" t="n">
         <v>7.43</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K20" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I21" t="n">
         <v>6.34</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K21" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I22" t="n">
         <v>5.25</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K22" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I23" t="n">
         <v>5.75</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="K23" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I24" t="n">
         <v>5.879999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K24" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I25" t="n">
         <v>6</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="K25" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I26" t="n">
         <v>6.18</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="K26" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I27" t="n">
         <v>5.87</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="K27" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I28" t="n">
         <v>6.239999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K28" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I29" t="n">
         <v>5.83</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="K29" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I30" t="n">
         <v>4.82</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K30" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I31" t="n">
         <v>3.44</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K31" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I32" t="n">
         <v>2.09</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="K32" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I33" t="n">
         <v>1.86</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K33" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I34" t="n">
         <v>1.72</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K34" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I35" t="n">
         <v>-0.1299999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="K35" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I36" t="n">
         <v>-0.27</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I37" t="n">
         <v>0.1500000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K37" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I38" t="n">
         <v>1.44</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K38" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I39" t="n">
         <v>1.26</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="K39" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I40" t="n">
         <v>3.68</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I41" t="n">
         <v>5.149999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="K41" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I42" t="n">
         <v>6.26</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K42" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I43" t="n">
         <v>10.22</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="K43" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I44" t="n">
         <v>10.73</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="K44" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I45" t="n">
         <v>10.74</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K45" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I46" t="n">
         <v>10.52</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K46" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I47" t="n">
         <v>10.71</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K47" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I48" t="n">
         <v>9.44</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I49" t="n">
         <v>7.449999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K49" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I50" t="n">
         <v>6.009999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="K50" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I51" t="n">
         <v>5.459999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="K51" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I52" t="n">
         <v>6.249999999999998</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K52" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I53" t="n">
         <v>7.969999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K53" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I54" t="n">
         <v>9.35</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I55" t="n">
         <v>11.83</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="K55" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I56" t="n">
         <v>11.92</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I57" t="n">
         <v>12.49</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K57" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I58" t="n">
         <v>13.76</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I59" t="n">
         <v>12.64</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="K59" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I60" t="n">
         <v>13.52</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K60" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I61" t="n">
         <v>16.06</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K61" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I62" t="n">
         <v>17.64</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K62" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I63" t="n">
         <v>20.12</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="K63" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I64" t="n">
         <v>22.13</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I65" t="n">
         <v>21.94</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I66" t="n">
         <v>21.55</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="K66" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I67" t="n">
         <v>22.05</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K67" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I68" t="n">
         <v>20.5</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K68" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I69" t="n">
         <v>19.64</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K69" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I70" t="n">
         <v>19.46</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="K70" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I71" t="n">
         <v>18.81</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K71" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I72" t="n">
         <v>20.08</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10525,13 +10537,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I73" t="n">
         <v>23.23</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K73" t="n">
@@ -10595,52 +10607,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40037</v>
       </c>
       <c r="C2" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="C3" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="C4" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="C5" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="C6" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="C7" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="C8" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="C12" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C13" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C14" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="C16" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C17" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C18" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C19" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="C20" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C21" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="C22" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="C23" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42052</v>
       </c>
       <c r="C24" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C25" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="C26" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C27" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="C28" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="C29" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C31" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="C32" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C36" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="C38" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C39" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="C40" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="C41" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C42" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C43" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="C44" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C45" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C46" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="C47" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="C48" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C49" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C50" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="C52" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C54" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="C56" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C57" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C59" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="C60" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C61" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C62" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C63" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C64" t="n">
@@ -12653,10 +12665,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C65" t="n">
@@ -12685,10 +12697,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C66" t="n">
@@ -12717,10 +12729,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="C67" t="n">
@@ -12749,10 +12761,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C68" t="n">
@@ -12781,10 +12793,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C69" t="n">
@@ -12813,10 +12825,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C70" t="n">
@@ -12863,12 +12875,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CAT.xlsx
+++ b/salidas/empresas/CAT.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>40.99885177612305</v>
+        <v>40.99884796142578</v>
       </c>
       <c r="C2" t="n">
         <v>67.90000152587891</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>44.12657928466797</v>
+        <v>44.12659454345703</v>
       </c>
       <c r="C3" t="n">
         <v>73.08000183105469</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>43.3597297668457</v>
+        <v>43.3597526550293</v>
       </c>
       <c r="C4" t="n">
         <v>71.80999755859375</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>45.87798690795898</v>
+        <v>45.87797546386719</v>
       </c>
       <c r="C5" t="n">
         <v>75.73999786376953</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>44.18798828125</v>
+        <v>44.18799209594727</v>
       </c>
       <c r="C6" t="n">
         <v>72.94999694824219</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>45.1147575378418</v>
+        <v>45.11476135253906</v>
       </c>
       <c r="C7" t="n">
         <v>74.48000335693359</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>43.11500930786133</v>
+        <v>43.11502075195312</v>
       </c>
       <c r="C8" t="n">
         <v>70.87000274658203</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>40.36518478393555</v>
+        <v>40.36518859863281</v>
       </c>
       <c r="C9" t="n">
         <v>66.34999847412109</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.03057861328125</v>
+        <v>40.03059768676758</v>
       </c>
       <c r="C10" t="n">
         <v>65.80000305175781</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>37.0950927734375</v>
+        <v>37.09507751464844</v>
       </c>
       <c r="C11" t="n">
         <v>60.70999908447266</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>37.90162658691406</v>
+        <v>37.90164184570312</v>
       </c>
       <c r="C12" t="n">
         <v>62.02999877929688</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>37.47391510009766</v>
+        <v>37.47393035888672</v>
       </c>
       <c r="C13" t="n">
         <v>61.33000183105469</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>39.56621551513672</v>
+        <v>39.56622314453125</v>
       </c>
       <c r="C15" t="n">
         <v>64.43000030517578</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>41.16287612915039</v>
+        <v>41.16286468505859</v>
       </c>
       <c r="C16" t="n">
         <v>67.02999877929688</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>44.78935623168945</v>
+        <v>44.78936004638672</v>
       </c>
       <c r="C17" t="n">
         <v>72.62000274658203</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>48.46529006958008</v>
+        <v>48.46527481079102</v>
       </c>
       <c r="C18" t="n">
         <v>78.58000183105469</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>48.29256820678711</v>
+        <v>48.29258346557617</v>
       </c>
       <c r="C19" t="n">
         <v>78.30000305175781</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>46.92755126953125</v>
+        <v>46.92753219604492</v>
       </c>
       <c r="C21" t="n">
         <v>75.76999664306641</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>48.57499313354492</v>
+        <v>48.57497024536133</v>
       </c>
       <c r="C22" t="n">
         <v>78.43000030517578</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>46.4257926940918</v>
+        <v>46.42580795288086</v>
       </c>
       <c r="C23" t="n">
         <v>74.61000061035156</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>44.7395133972168</v>
+        <v>44.73949813842773</v>
       </c>
       <c r="C24" t="n">
         <v>71.90000152587891</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>45.15018844604492</v>
+        <v>45.15019226074219</v>
       </c>
       <c r="C25" t="n">
         <v>72.55999755859375</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>44.42210006713867</v>
+        <v>44.42208480834961</v>
       </c>
       <c r="C26" t="n">
         <v>70.98999786376953</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>45.26060485839844</v>
+        <v>45.26058197021484</v>
       </c>
       <c r="C27" t="n">
         <v>72.33000183105469</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>51.47099685668945</v>
+        <v>51.47102355957031</v>
       </c>
       <c r="C29" t="n">
         <v>81.87999725341797</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>51.94875335693359</v>
+        <v>51.94873046875</v>
       </c>
       <c r="C30" t="n">
         <v>82.63999938964844</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>46.40436935424805</v>
+        <v>46.40437316894531</v>
       </c>
       <c r="C31" t="n">
         <v>73.81999969482422</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>43.96310424804688</v>
+        <v>43.96313095092773</v>
       </c>
       <c r="C32" t="n">
         <v>69.51999664306641</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.68990325927734</v>
+        <v>37.68990707397461</v>
       </c>
       <c r="C34" t="n">
         <v>59.59999847412109</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>24.40060615539551</v>
+        <v>24.40060997009277</v>
       </c>
       <c r="C35" t="n">
         <v>38.20000076293945</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>26.18275451660156</v>
+        <v>26.18274688720703</v>
       </c>
       <c r="C36" t="n">
         <v>40.9900016784668</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>28.53339195251465</v>
+        <v>28.53337860107422</v>
       </c>
       <c r="C37" t="n">
         <v>44.66999816894531</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.91831970214844</v>
+        <v>19.9183292388916</v>
       </c>
       <c r="C38" t="n">
         <v>30.85000038146973</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.88946151733398</v>
+        <v>15.88946723937988</v>
       </c>
       <c r="C39" t="n">
         <v>24.61000061035156</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>18.05238914489746</v>
+        <v>18.05239486694336</v>
       </c>
       <c r="C40" t="n">
         <v>27.95999908447266</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>23.26821708679199</v>
+        <v>23.26821517944336</v>
       </c>
       <c r="C41" t="n">
         <v>35.58000183105469</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>23.18974113464355</v>
+        <v>23.18974494934082</v>
       </c>
       <c r="C42" t="n">
         <v>35.45999908447266</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.60713386535645</v>
+        <v>21.60713005065918</v>
       </c>
       <c r="C43" t="n">
         <v>33.04000091552734</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>30.00370979309082</v>
+        <v>30.00371360778809</v>
       </c>
       <c r="C45" t="n">
         <v>45.31000137329102</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>33.99009704589844</v>
+        <v>33.99010848999023</v>
       </c>
       <c r="C46" t="n">
         <v>51.33000183105469</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>36.72415924072266</v>
+        <v>36.72415542602539</v>
       </c>
       <c r="C47" t="n">
         <v>55.06000137329102</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>38.94521331787109</v>
+        <v>38.94522476196289</v>
       </c>
       <c r="C48" t="n">
         <v>58.38999938964844</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>38.01145553588867</v>
+        <v>38.01142883300781</v>
       </c>
       <c r="C49" t="n">
         <v>56.9900016784668</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>35.08098602294922</v>
+        <v>35.08100128173828</v>
       </c>
       <c r="C50" t="n">
         <v>52.2400016784668</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>38.31106567382812</v>
+        <v>38.31106948852539</v>
       </c>
       <c r="C51" t="n">
         <v>57.04999923706055</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.20597457885742</v>
+        <v>42.20596694946289</v>
       </c>
       <c r="C52" t="n">
         <v>62.84999847412109</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>46.01004791259766</v>
+        <v>46.01003265380859</v>
       </c>
       <c r="C53" t="n">
         <v>68.08999633789062</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.59073638916016</v>
+        <v>40.59073257446289</v>
       </c>
       <c r="C55" t="n">
         <v>60.06999969482422</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>47.44561767578125</v>
+        <v>47.44564437866211</v>
       </c>
       <c r="C56" t="n">
         <v>69.75</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>53.52002716064453</v>
+        <v>53.52001571655273</v>
       </c>
       <c r="C58" t="n">
         <v>78.68000030517578</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>64.06070709228516</v>
+        <v>64.06072235107422</v>
       </c>
       <c r="C61" t="n">
         <v>93.66000366210938</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>66.66401672363281</v>
+        <v>66.66403198242188</v>
       </c>
       <c r="C62" t="n">
         <v>97.01000213623047</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>76.51828002929688</v>
+        <v>76.518310546875</v>
       </c>
       <c r="C64" t="n">
         <v>111.3499984741211</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>79.63852691650391</v>
+        <v>79.63853454589844</v>
       </c>
       <c r="C65" t="n">
         <v>115.4100036621094</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>73.00715637207031</v>
+        <v>73.00714874267578</v>
       </c>
       <c r="C66" t="n">
         <v>105.8000030517578</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>73.46257781982422</v>
+        <v>73.46257019042969</v>
       </c>
       <c r="C67" t="n">
         <v>106.4599990844727</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>68.45787811279297</v>
+        <v>68.45787048339844</v>
       </c>
       <c r="C68" t="n">
         <v>98.79000091552734</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>63.05968475341797</v>
+        <v>63.05968856811523</v>
       </c>
       <c r="C69" t="n">
         <v>91</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>51.16843032836914</v>
+        <v>51.16842651367188</v>
       </c>
       <c r="C70" t="n">
         <v>73.83999633789062</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>65.81967926025391</v>
+        <v>65.81968688964844</v>
       </c>
       <c r="C71" t="n">
         <v>94.45999908447266</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>68.20272827148438</v>
+        <v>68.20271301269531</v>
       </c>
       <c r="C72" t="n">
         <v>97.87999725341797</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>63.13003158569336</v>
+        <v>63.13004684448242</v>
       </c>
       <c r="C73" t="n">
         <v>90.59999847412109</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>79.93720245361328</v>
+        <v>79.93721008300781</v>
       </c>
       <c r="C75" t="n">
         <v>114.2099990844727</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>74.55484771728516</v>
+        <v>74.55487060546875</v>
       </c>
       <c r="C76" t="n">
         <v>106.5199966430664</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>72.23445129394531</v>
+        <v>72.23442840576172</v>
       </c>
       <c r="C77" t="n">
         <v>102.7699966430664</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>61.58587646484375</v>
+        <v>61.58589172363281</v>
       </c>
       <c r="C78" t="n">
         <v>87.62000274658203</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>59.68108749389648</v>
+        <v>59.68109512329102</v>
       </c>
       <c r="C79" t="n">
         <v>84.91000366210938</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>59.56725311279297</v>
+        <v>59.56723785400391</v>
       </c>
       <c r="C80" t="n">
         <v>84.20999908447266</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>60.35947799682617</v>
+        <v>60.35948944091797</v>
       </c>
       <c r="C81" t="n">
         <v>85.33000183105469</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>60.86172103881836</v>
+        <v>60.86171340942383</v>
       </c>
       <c r="C82" t="n">
         <v>86.04000091552734</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>60.35394668579102</v>
+        <v>60.35394287109375</v>
       </c>
       <c r="C83" t="n">
         <v>84.80999755859375</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>60.65994262695312</v>
+        <v>60.65993118286133</v>
       </c>
       <c r="C84" t="n">
         <v>85.23999786376953</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>64.13713073730469</v>
+        <v>64.13713836669922</v>
       </c>
       <c r="C85" t="n">
         <v>89.61000061035156</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>70.42129516601562</v>
+        <v>70.42131042480469</v>
       </c>
       <c r="C86" t="n">
         <v>98.38999938964844</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>66.11255645751953</v>
+        <v>66.11257934570312</v>
       </c>
       <c r="C87" t="n">
         <v>92.37000274658203</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>62.24761581420898</v>
+        <v>62.24758529663086</v>
       </c>
       <c r="C88" t="n">
         <v>86.97000122070312</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>60.99069213867188</v>
+        <v>60.99068832397461</v>
       </c>
       <c r="C89" t="n">
         <v>84.66999816894531</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>61.80466842651367</v>
+        <v>61.80464935302734</v>
       </c>
       <c r="C90" t="n">
         <v>85.80000305175781</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>59.42037582397461</v>
+        <v>59.42036437988281</v>
       </c>
       <c r="C91" t="n">
         <v>82.48999786376953</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>60.13925170898438</v>
+        <v>60.13923263549805</v>
       </c>
       <c r="C92" t="n">
         <v>82.91000366210938</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>59.8708610534668</v>
+        <v>59.8708381652832</v>
       </c>
       <c r="C93" t="n">
         <v>82.54000091552734</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>60.49466705322266</v>
+        <v>60.49465179443359</v>
       </c>
       <c r="C94" t="n">
         <v>83.40000152587891</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>60.88914108276367</v>
+        <v>60.88913726806641</v>
       </c>
       <c r="C95" t="n">
         <v>83.36000061035156</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>61.79486846923828</v>
+        <v>61.79485702514648</v>
       </c>
       <c r="C96" t="n">
         <v>84.59999847412109</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>66.33084869384766</v>
+        <v>66.33084106445312</v>
       </c>
       <c r="C97" t="n">
         <v>90.80999755859375</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>71.29322814941406</v>
+        <v>71.29325866699219</v>
       </c>
       <c r="C99" t="n">
         <v>96.97000122070312</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>73.0577392578125</v>
+        <v>73.05773162841797</v>
       </c>
       <c r="C100" t="n">
         <v>99.37000274658203</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>77.94732666015625</v>
+        <v>77.94731903076172</v>
       </c>
       <c r="C101" t="n">
         <v>105.4000015258789</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>75.60299682617188</v>
+        <v>75.60301971435547</v>
       </c>
       <c r="C102" t="n">
         <v>102.2300033569336</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>80.36560821533203</v>
+        <v>80.36563110351562</v>
       </c>
       <c r="C103" t="n">
         <v>108.6699981689453</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.97963714599609</v>
+        <v>74.97962188720703</v>
       </c>
       <c r="C104" t="n">
         <v>100.75</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>81.17146301269531</v>
+        <v>81.17150115966797</v>
       </c>
       <c r="C105" t="n">
         <v>109.0699996948242</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>73.6995849609375</v>
+        <v>73.69957733154297</v>
       </c>
       <c r="C106" t="n">
         <v>99.02999877929688</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.04573822021484</v>
+        <v>76.04570007324219</v>
       </c>
       <c r="C107" t="n">
         <v>101.4100036621094</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>75.43834686279297</v>
+        <v>75.43830108642578</v>
       </c>
       <c r="C108" t="n">
         <v>100.5999984741211</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>68.63686370849609</v>
+        <v>68.63689422607422</v>
       </c>
       <c r="C109" t="n">
         <v>91.52999877929688</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>60.45993041992188</v>
+        <v>60.4599494934082</v>
       </c>
       <c r="C110" t="n">
         <v>79.97000122070312</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>62.67512512207031</v>
+        <v>62.67511749267578</v>
       </c>
       <c r="C111" t="n">
         <v>82.90000152587891</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>60.50528335571289</v>
+        <v>60.50528717041016</v>
       </c>
       <c r="C112" t="n">
         <v>80.02999877929688</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>66.22850036621094</v>
+        <v>66.22849273681641</v>
       </c>
       <c r="C113" t="n">
         <v>86.87999725341797</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>65.03931427001953</v>
+        <v>65.03932189941406</v>
       </c>
       <c r="C114" t="n">
         <v>85.31999969482422</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>64.65815734863281</v>
+        <v>64.65819549560547</v>
       </c>
       <c r="C115" t="n">
         <v>84.81999969482422</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>60.49299621582031</v>
+        <v>60.49300384521484</v>
       </c>
       <c r="C116" t="n">
         <v>78.62999725341797</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>58.80815887451172</v>
+        <v>58.80815505981445</v>
       </c>
       <c r="C117" t="n">
         <v>76.44000244140625</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>50.28390502929688</v>
+        <v>50.28390121459961</v>
       </c>
       <c r="C118" t="n">
         <v>65.36000061035156</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.78149795532227</v>
+        <v>56.78152084350586</v>
       </c>
       <c r="C119" t="n">
         <v>72.98999786376953</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>56.51700210571289</v>
+        <v>56.51700592041016</v>
       </c>
       <c r="C120" t="n">
         <v>72.65000152587891</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>49.02490615844727</v>
+        <v>49.0249137878418</v>
       </c>
       <c r="C122" t="n">
         <v>62.2400016784668</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>53.32561492919922</v>
+        <v>53.32561874389648</v>
       </c>
       <c r="C123" t="n">
         <v>67.69999694824219</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.28867721557617</v>
+        <v>60.28868103027344</v>
       </c>
       <c r="C124" t="n">
         <v>76.54000091552734</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>61.81502151489258</v>
+        <v>61.81502914428711</v>
       </c>
       <c r="C125" t="n">
         <v>77.72000122070312</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.67125701904297</v>
+        <v>57.67123413085938</v>
       </c>
       <c r="C126" t="n">
         <v>72.51000213623047</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.2959098815918</v>
+        <v>60.29591369628906</v>
       </c>
       <c r="C127" t="n">
         <v>75.80999755859375</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>71.28386688232422</v>
+        <v>71.28388977050781</v>
       </c>
       <c r="C130" t="n">
         <v>88.76999664306641</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>67.61146545410156</v>
+        <v>67.61145782470703</v>
       </c>
       <c r="C131" t="n">
         <v>83.45999908447266</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>77.41372680664062</v>
+        <v>77.41373443603516</v>
       </c>
       <c r="C132" t="n">
         <v>95.55999755859375</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>78.95457458496094</v>
+        <v>78.95458221435547</v>
       </c>
       <c r="C135" t="n">
         <v>96.66000366210938</v>
@@ -3880,7 +3880,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>75.76895904541016</v>
+        <v>75.76895141601562</v>
       </c>
       <c r="C136" t="n">
         <v>92.76000213623047</v>
@@ -3934,7 +3934,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>86.83349609375</v>
+        <v>86.83348846435547</v>
       </c>
       <c r="C138" t="n">
         <v>105.4300003051758</v>
@@ -3961,7 +3961,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>88.50541687011719</v>
+        <v>88.50540924072266</v>
       </c>
       <c r="C139" t="n">
         <v>107.4599990844727</v>
@@ -4015,7 +4015,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>97.46475219726562</v>
+        <v>97.46475982666016</v>
       </c>
       <c r="C141" t="n">
         <v>117.4899978637695</v>
@@ -4044,7 +4044,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>103.4541397094727</v>
+        <v>103.4541625976562</v>
       </c>
       <c r="C142" t="n">
         <v>124.7099990844727</v>
@@ -4073,7 +4073,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>113.3258666992188</v>
+        <v>113.3258743286133</v>
       </c>
       <c r="C143" t="n">
         <v>135.8000030517578</v>
@@ -4102,7 +4102,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>117.7904815673828</v>
+        <v>117.7904968261719</v>
       </c>
       <c r="C144" t="n">
         <v>141.1499938964844</v>
@@ -4131,7 +4131,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>131.5013885498047</v>
+        <v>131.5014495849609</v>
       </c>
       <c r="C145" t="n">
         <v>157.5800018310547</v>
@@ -4160,7 +4160,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>136.4713134765625</v>
+        <v>136.4713745117188</v>
       </c>
       <c r="C146" t="n">
         <v>162.7799987792969</v>
@@ -4189,7 +4189,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>129.6385040283203</v>
+        <v>129.6385650634766</v>
       </c>
       <c r="C147" t="n">
         <v>154.6300048828125</v>
@@ -4218,7 +4218,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>123.5603256225586</v>
+        <v>123.5603103637695</v>
       </c>
       <c r="C148" t="n">
         <v>147.3800048828125</v>
@@ -4276,7 +4276,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>127.9993743896484</v>
+        <v>127.9993591308594</v>
       </c>
       <c r="C150" t="n">
         <v>151.9100036621094</v>
@@ -4305,7 +4305,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>114.3155746459961</v>
+        <v>114.3155670166016</v>
       </c>
       <c r="C151" t="n">
         <v>135.6699981689453</v>
@@ -4334,7 +4334,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>121.9088516235352</v>
+        <v>121.9088287353516</v>
       </c>
       <c r="C152" t="n">
         <v>143.8000030517578</v>
@@ -4363,7 +4363,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>117.7123718261719</v>
+        <v>117.7124099731445</v>
       </c>
       <c r="C153" t="n">
         <v>138.8500061035156</v>
@@ -4392,7 +4392,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>129.2759399414062</v>
+        <v>129.2759246826172</v>
       </c>
       <c r="C154" t="n">
         <v>152.4900054931641</v>
@@ -4421,7 +4421,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>103.5065307617188</v>
+        <v>103.5065460205078</v>
       </c>
       <c r="C155" t="n">
         <v>121.3199996948242</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>115.7495040893555</v>
+        <v>115.7495269775391</v>
       </c>
       <c r="C156" t="n">
         <v>135.6699981689453</v>
@@ -4479,7 +4479,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>108.4122543334961</v>
+        <v>108.4122695922852</v>
       </c>
       <c r="C157" t="n">
         <v>127.0699996948242</v>
@@ -4508,7 +4508,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>114.3389205932617</v>
+        <v>114.3389282226562</v>
       </c>
       <c r="C158" t="n">
         <v>133.1600036621094</v>
@@ -4537,7 +4537,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>117.9281005859375</v>
+        <v>117.9281234741211</v>
       </c>
       <c r="C159" t="n">
         <v>137.3399963378906</v>
@@ -4566,7 +4566,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>116.3396301269531</v>
+        <v>116.3396224975586</v>
       </c>
       <c r="C160" t="n">
         <v>135.4900054931641</v>
@@ -4595,7 +4595,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>120.4397659301758</v>
+        <v>120.4397735595703</v>
       </c>
       <c r="C161" t="n">
         <v>139.4199981689453</v>
@@ -4653,7 +4653,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>117.7358932495117</v>
+        <v>117.7358779907227</v>
       </c>
       <c r="C163" t="n">
         <v>136.2899932861328</v>
@@ -4682,7 +4682,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>114.6200561523438</v>
+        <v>114.6200714111328</v>
       </c>
       <c r="C164" t="n">
         <v>131.6699981689453</v>
@@ -4711,7 +4711,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>103.590690612793</v>
+        <v>103.590705871582</v>
       </c>
       <c r="C165" t="n">
         <v>119</v>
@@ -4740,7 +4740,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>109.9541397094727</v>
+        <v>109.9541320800781</v>
       </c>
       <c r="C166" t="n">
         <v>126.3099975585938</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>120.8991851806641</v>
+        <v>120.8992004394531</v>
       </c>
       <c r="C167" t="n">
         <v>137.8000030517578</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>126.9792633056641</v>
+        <v>126.9791641235352</v>
       </c>
       <c r="C168" t="n">
         <v>144.7299957275391</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>116.0485992431641</v>
+        <v>116.0485916137695</v>
       </c>
       <c r="C170" t="n">
         <v>131.3500061035156</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>109.7668685913086</v>
+        <v>109.7668533325195</v>
       </c>
       <c r="C171" t="n">
         <v>124.2399978637695</v>
@@ -4914,7 +4914,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>102.5221099853516</v>
+        <v>102.5221252441406</v>
       </c>
       <c r="C172" t="n">
         <v>116.0400009155273</v>
@@ -4943,7 +4943,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>103.7664947509766</v>
+        <v>103.7665023803711</v>
       </c>
       <c r="C173" t="n">
         <v>116.379997253418</v>
@@ -5001,7 +5001,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>112.7896575927734</v>
+        <v>112.7896957397461</v>
       </c>
       <c r="C175" t="n">
         <v>126.5</v>
@@ -5030,7 +5030,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>119.3655319213867</v>
+        <v>119.3655471801758</v>
       </c>
       <c r="C176" t="n">
         <v>132.8800048828125</v>
@@ -5059,7 +5059,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>127.8364334106445</v>
+        <v>127.8364486694336</v>
       </c>
       <c r="C177" t="n">
         <v>142.3099975585938</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>141.9389953613281</v>
+        <v>141.9390563964844</v>
       </c>
       <c r="C179" t="n">
         <v>157.0500030517578</v>
@@ -5175,7 +5175,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>164.5065155029297</v>
+        <v>164.5064544677734</v>
       </c>
       <c r="C181" t="n">
         <v>182.0200042724609</v>
@@ -5204,7 +5204,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>166.1268005371094</v>
+        <v>166.1268157958984</v>
       </c>
       <c r="C182" t="n">
         <v>182.8399963378906</v>
@@ -5262,7 +5262,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>210.6750183105469</v>
+        <v>210.6749877929688</v>
       </c>
       <c r="C184" t="n">
         <v>231.8699951171875</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>208.1955718994141</v>
+        <v>208.1955413818359</v>
       </c>
       <c r="C185" t="n">
         <v>228.1100006103516</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>220.0332489013672</v>
+        <v>220.0332336425781</v>
       </c>
       <c r="C186" t="n">
         <v>241.0800018310547</v>
@@ -5349,7 +5349,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>198.6305084228516</v>
+        <v>198.6304321289062</v>
       </c>
       <c r="C187" t="n">
         <v>217.6300048828125</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>189.7129821777344</v>
+        <v>189.7129516601562</v>
       </c>
       <c r="C188" t="n">
         <v>206.75</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>193.4934844970703</v>
+        <v>193.4934692382812</v>
       </c>
       <c r="C189" t="n">
         <v>210.8699951171875</v>
@@ -5465,7 +5465,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>188.2323608398438</v>
+        <v>188.232421875</v>
       </c>
       <c r="C191" t="n">
         <v>204.0099945068359</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>178.3968200683594</v>
+        <v>178.3968048095703</v>
       </c>
       <c r="C192" t="n">
         <v>193.3500061035156</v>
@@ -5523,7 +5523,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>190.7512969970703</v>
+        <v>190.7512817382812</v>
       </c>
       <c r="C193" t="n">
         <v>206.7400054931641</v>
@@ -5552,7 +5552,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>186.8742218017578</v>
+        <v>186.874267578125</v>
       </c>
       <c r="C194" t="n">
         <v>201.5599975585938</v>
@@ -5581,7 +5581,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>173.9128265380859</v>
+        <v>173.912841796875</v>
       </c>
       <c r="C195" t="n">
         <v>187.5800018310547</v>
@@ -5610,7 +5610,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>206.5852355957031</v>
+        <v>206.5852508544922</v>
       </c>
       <c r="C196" t="n">
         <v>222.8200073242188</v>
@@ -5668,7 +5668,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>201.0827941894531</v>
+        <v>201.0828247070312</v>
       </c>
       <c r="C198" t="n">
         <v>215.8500061035156</v>
@@ -5697,7 +5697,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>166.5302886962891</v>
+        <v>166.5302734375</v>
       </c>
       <c r="C199" t="n">
         <v>178.7599945068359</v>
@@ -5726,7 +5726,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>185.9732666015625</v>
+        <v>185.9732055664062</v>
       </c>
       <c r="C200" t="n">
         <v>198.25</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>173.271728515625</v>
+        <v>173.2717132568359</v>
       </c>
       <c r="C201" t="n">
         <v>184.7100067138672</v>
@@ -5813,7 +5813,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>204.4142913818359</v>
+        <v>204.4142608642578</v>
       </c>
       <c r="C203" t="n">
         <v>216.4600067138672</v>
@@ -5842,7 +5842,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>223.2540740966797</v>
+        <v>223.2540893554688</v>
       </c>
       <c r="C204" t="n">
         <v>236.4100036621094</v>
@@ -5871,7 +5871,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>226.2287902832031</v>
+        <v>226.2288055419922</v>
       </c>
       <c r="C205" t="n">
         <v>239.5599975585938</v>
@@ -5929,7 +5929,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>227.2982025146484</v>
+        <v>227.2981872558594</v>
       </c>
       <c r="C207" t="n">
         <v>239.5500030517578</v>
@@ -5987,7 +5987,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>208.7363891601562</v>
+        <v>208.7364044189453</v>
       </c>
       <c r="C209" t="n">
         <v>218.8000030517578</v>
@@ -6016,7 +6016,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>196.2866058349609</v>
+        <v>196.28662109375</v>
       </c>
       <c r="C210" t="n">
         <v>205.75</v>
@@ -6045,7 +6045,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>234.7330322265625</v>
+        <v>234.7330169677734</v>
       </c>
       <c r="C211" t="n">
         <v>246.0500030517578</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>269.5277099609375</v>
+        <v>269.5277404785156</v>
       </c>
       <c r="C213" t="n">
         <v>281.1300048828125</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>217.8407287597656</v>
+        <v>217.8407440185547</v>
       </c>
       <c r="C215" t="n">
         <v>226.0500030517578</v>
@@ -6219,7 +6219,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>284.9324035644531</v>
+        <v>284.932373046875</v>
       </c>
       <c r="C217" t="n">
         <v>295.6700134277344</v>
@@ -6248,7 +6248,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>290.74462890625</v>
+        <v>290.7446594238281</v>
       </c>
       <c r="C218" t="n">
         <v>300.3099975585938</v>
@@ -6306,7 +6306,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>354.7585754394531</v>
+        <v>354.7586364746094</v>
       </c>
       <c r="C220" t="n">
         <v>366.4299926757812</v>
@@ -6335,7 +6335,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>325.0941467285156</v>
+        <v>325.0941772460938</v>
       </c>
       <c r="C221" t="n">
         <v>334.5700073242188</v>
@@ -6393,7 +6393,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>323.6658020019531</v>
+        <v>323.6658325195312</v>
       </c>
       <c r="C223" t="n">
         <v>333.1000061035156</v>
@@ -6422,7 +6422,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>337.7647399902344</v>
+        <v>337.7648010253906</v>
       </c>
       <c r="C224" t="n">
         <v>346.2000122070312</v>
@@ -6451,7 +6451,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>347.423583984375</v>
+        <v>347.4235229492188</v>
       </c>
       <c r="C225" t="n">
         <v>356.1000061035156</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>381.5903015136719</v>
+        <v>381.5902404785156</v>
       </c>
       <c r="C226" t="n">
         <v>391.1199951171875</v>
@@ -6509,7 +6509,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>368.3524780273438</v>
+        <v>368.3525390625</v>
       </c>
       <c r="C227" t="n">
         <v>376.2000122070312</v>
@@ -6538,7 +6538,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>397.6385192871094</v>
+        <v>397.6385498046875</v>
       </c>
       <c r="C228" t="n">
         <v>406.1099853515625</v>
@@ -6567,7 +6567,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>355.1928405761719</v>
+        <v>355.19287109375</v>
       </c>
       <c r="C229" t="n">
         <v>362.760009765625</v>
@@ -6770,7 +6770,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>434.1123046875</v>
+        <v>434.1122741699219</v>
       </c>
       <c r="C236" t="n">
         <v>438.0199890136719</v>
@@ -6857,7 +6857,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>573.7538452148438</v>
+        <v>573.7537841796875</v>
       </c>
       <c r="C239" t="n">
         <v>577.260009765625</v>
@@ -6915,7 +6915,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>569.3904418945312</v>
+        <v>569.3905029296875</v>
       </c>
       <c r="C241" t="n">
         <v>572.8699951171875</v>
@@ -6944,7 +6944,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>654.8959350585938</v>
+        <v>654.89599609375</v>
       </c>
       <c r="C242" t="n">
         <v>657.3599853515625</v>
@@ -6973,7 +6973,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>740.0455932617188</v>
+        <v>740.045654296875</v>
       </c>
       <c r="C243" t="n">
         <v>742.8300170898438</v>
@@ -7002,7 +7002,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>705.804443359375</v>
+        <v>705.8045043945312</v>
       </c>
       <c r="C244" t="n">
         <v>708.4600219726562</v>
